--- a/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>102</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.16039</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-74.22819</v>
-      </c>
-      <c r="I2" t="n">
-        <v>306</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.16039</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-74.22819</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>GUAMAN POMA DE AYALA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.14966</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-74.21810000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>660</v>
-      </c>
-      <c r="J3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.14966</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-74.2181</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>320 SAN MIGUELITO ARCANGEL</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.15368</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-74.22856</v>
-      </c>
-      <c r="I4" t="n">
-        <v>306</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.15368</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-74.22856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>331JARDIN DE NIÑOS / NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.16448</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-74.22664</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1297</v>
-      </c>
-      <c r="J5" t="n">
-        <v>66</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.16448</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-74.22664</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>LUIS CARRANZA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.15696</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-74.22479</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1668</v>
-      </c>
-      <c r="J6" t="n">
-        <v>80</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.15696</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-74.22479</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1668</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>MARISCAL CACERES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.15031</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-74.22324</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4254</v>
-      </c>
-      <c r="J7" t="n">
-        <v>184</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.15031</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-74.22324</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>38006 9 DE DICIEMBRE</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.15892</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-74.224053</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1167</v>
-      </c>
-      <c r="J8" t="n">
-        <v>61</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.15892</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-74.224053</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>38018 / 38018 DE MARAVILLAS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.15254</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-74.22561</v>
-      </c>
-      <c r="I9" t="n">
-        <v>639</v>
-      </c>
-      <c r="J9" t="n">
-        <v>31</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.15254</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-74.22561</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>LOS LIBERTADORES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.15725</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.23076</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J10" t="n">
-        <v>65</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.15725</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.23076</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>38001 GUSTAVO CASTRO PANTOJA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.16038</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-74.2277</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1157</v>
-      </c>
-      <c r="J11" t="n">
-        <v>51</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.16038</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-74.2277</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>MELITON CARVAJAL</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.16403</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-74.2338</v>
-      </c>
-      <c r="I12" t="n">
-        <v>921</v>
-      </c>
-      <c r="J12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.16403</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-74.2338</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>38059 ABILIO SOTO YUPANQUI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.15826</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-74.235</v>
-      </c>
-      <c r="I13" t="n">
-        <v>261</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.15826</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-74.235</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>39001 MARISCAL SUCRE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.16193</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-74.22535999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>507</v>
-      </c>
-      <c r="J14" t="n">
-        <v>25</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.16193</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-74.22536</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>39002 MARIA PARADO DE BELLIDO / MARIA PARADO DE BELIDO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.15927</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-74.22838</v>
-      </c>
-      <c r="I15" t="n">
-        <v>883</v>
-      </c>
-      <c r="J15" t="n">
-        <v>47</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.15927</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-74.22838</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>39003 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.15366</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-74.23147</v>
-      </c>
-      <c r="I16" t="n">
-        <v>753</v>
-      </c>
-      <c r="J16" t="n">
-        <v>36</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.15366</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-74.23147</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>SAN RAMON</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.17085</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-74.22765</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2396</v>
-      </c>
-      <c r="J17" t="n">
-        <v>120</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.17085</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-74.22765</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2396</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.162192</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-74.23324</v>
-      </c>
-      <c r="I18" t="n">
-        <v>224</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.162192</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-74.23324</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>38083</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.14571</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-74.22732999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>636</v>
-      </c>
-      <c r="J19" t="n">
-        <v>29</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.14571</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-74.22733</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>SANTA MARIA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-13.15647</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-74.22566999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>272</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-13.15647</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-74.22567</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-13.15919</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-74.22801</v>
-      </c>
-      <c r="I21" t="n">
-        <v>697</v>
-      </c>
-      <c r="J21" t="n">
-        <v>36</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-13.15919</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-74.22801</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.1601</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-74.22105999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>524</v>
-      </c>
-      <c r="J22" t="n">
-        <v>35</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.1601</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-74.22106</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>FEDERICO FROEBEL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.14883</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-74.22832</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1537</v>
-      </c>
-      <c r="J23" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.14883</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-74.22832</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SAN ANTONIO DE HUAMANGA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-13.16366</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-74.22599</v>
-      </c>
-      <c r="I24" t="n">
-        <v>937</v>
-      </c>
-      <c r="J24" t="n">
-        <v>57</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-13.16366</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-74.22599</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-13.16004</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-74.22431</v>
-      </c>
-      <c r="I25" t="n">
-        <v>950</v>
-      </c>
-      <c r="J25" t="n">
-        <v>46</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-13.16004</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-74.22431</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>EL NAZARENO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-13.158519</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-74.22724700000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>215</v>
-      </c>
-      <c r="J26" t="n">
-        <v>15</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-13.158519</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-74.227247</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-13.16472</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-74.22872</v>
-      </c>
-      <c r="I27" t="n">
-        <v>328</v>
-      </c>
-      <c r="J27" t="n">
-        <v>25</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-13.16472</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-74.22872</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-13.15667</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-74.22546</v>
-      </c>
-      <c r="I28" t="n">
-        <v>230</v>
-      </c>
-      <c r="J28" t="n">
-        <v>25</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-13.15667</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-74.22546</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>LEONARDO DA VINCI</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-13.1592</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-74.22828</v>
-      </c>
-      <c r="I29" t="n">
-        <v>261</v>
-      </c>
-      <c r="J29" t="n">
-        <v>17</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-13.1592</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-74.22828</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>38582 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-13.1806</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-74.221</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1214</v>
-      </c>
-      <c r="J30" t="n">
-        <v>59</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-13.1806</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-74.221</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>38037 LIBERTAD DE AMERICA / LIBERTAD DE AMERICA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-13.053175</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-74.140672</v>
-      </c>
-      <c r="I31" t="n">
-        <v>617</v>
-      </c>
-      <c r="J31" t="n">
-        <v>54</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-13.053175</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-74.140672</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>38984-12 CARLOS LABORDE</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-13.13955</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-74.22659</v>
-      </c>
-      <c r="I32" t="n">
-        <v>641</v>
-      </c>
-      <c r="J32" t="n">
-        <v>36</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-13.13955</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-74.22659</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>39007 SEÑOR DE AGONIA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-13.15339</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-74.21884</v>
-      </c>
-      <c r="I33" t="n">
-        <v>354</v>
-      </c>
-      <c r="J33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-13.15339</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-74.21884</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-13.166</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-74.22751</v>
-      </c>
-      <c r="I34" t="n">
-        <v>353</v>
-      </c>
-      <c r="J34" t="n">
-        <v>11</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-13.166</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-74.22751</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-13.12064</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-74.2317</v>
-      </c>
-      <c r="I35" t="n">
-        <v>266</v>
-      </c>
-      <c r="J35" t="n">
-        <v>15</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-13.12064</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-74.2317</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>DISCOVERY</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-13.16185</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-74.22750000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>244</v>
-      </c>
-      <c r="J36" t="n">
-        <v>15</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-13.16185</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-74.2275</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-13.15732</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-74.22499999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>703</v>
-      </c>
-      <c r="J37" t="n">
-        <v>38</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-13.15732</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-74.225</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-13.16532</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-74.22931</v>
-      </c>
-      <c r="I38" t="n">
-        <v>264</v>
-      </c>
-      <c r="J38" t="n">
-        <v>18</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-13.16532</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-74.22931</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>38984-15 SAN JUAN DE LA FRONTERA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-13.129448</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-74.22683499999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>228</v>
-      </c>
-      <c r="J39" t="n">
-        <v>16</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-13.129448</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-74.226835</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>REPUBLICA BOLIVARIANA DE VENEZUELA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-13.135569</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-74.232699</v>
-      </c>
-      <c r="I40" t="n">
-        <v>727</v>
-      </c>
-      <c r="J40" t="n">
-        <v>45</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-13.135569</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-74.232699</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>CARICIAS Y TERNURAS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-13.1551</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-74.22929999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>255</v>
-      </c>
-      <c r="J41" t="n">
-        <v>17</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-13.1551</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-74.2293</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SAN ISIDRO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-13.14993</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-74.22572</v>
-      </c>
-      <c r="I42" t="n">
-        <v>64</v>
-      </c>
-      <c r="J42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-13.14993</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-74.22572</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-13.16322</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-74.2235</v>
-      </c>
-      <c r="I43" t="n">
-        <v>237</v>
-      </c>
-      <c r="J43" t="n">
-        <v>13</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-13.16322</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-74.2235</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>432-91</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-13.15728</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-74.23635</v>
-      </c>
-      <c r="I44" t="n">
-        <v>71</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-13.15728</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-74.23635</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>LOS LICENCIADOS</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-13.14587</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-74.22923</v>
-      </c>
-      <c r="I45" t="n">
-        <v>593</v>
-      </c>
-      <c r="J45" t="n">
-        <v>36</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-13.14587</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-74.22923</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>COAR AYACUCHO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-13.17009</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-74.22819</v>
-      </c>
-      <c r="I46" t="n">
-        <v>235</v>
-      </c>
-      <c r="J46" t="n">
-        <v>21</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-13.17009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-74.22819</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>SAN ISIDRO</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-13.14993</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-74.22575000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>62</v>
-      </c>
-      <c r="J47" t="n">
-        <v>9</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-13.14993</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-74.22575</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>LOBACHEVSKI</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-13.15589</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-74.22627</v>
-      </c>
-      <c r="I48" t="n">
-        <v>258</v>
-      </c>
-      <c r="J48" t="n">
-        <v>27</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-13.15589</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-74.22627</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>CENTER</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-13.15642</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-74.22682</v>
-      </c>
-      <c r="I49" t="n">
-        <v>300</v>
-      </c>
-      <c r="J49" t="n">
-        <v>18</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-13.15642</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-74.22682</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>CYBERNET</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-13.168671</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-74.227322</v>
-      </c>
-      <c r="I50" t="n">
-        <v>569</v>
-      </c>
-      <c r="J50" t="n">
-        <v>24</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-13.168671</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-74.227322</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>EL TAMBOR DE HOJALATA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-13.15653</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-74.22686</v>
-      </c>
-      <c r="I51" t="n">
-        <v>242</v>
-      </c>
-      <c r="J51" t="n">
-        <v>19</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-13.15653</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-74.22686</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73925</t>
+          <t>397963</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.16039</t>
+          <t>-13.166</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.22819</t>
+          <t>-74.22751</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>74388</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GUAMAN POMA DE AYALA</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.14966</t>
+          <t>-13.17085</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.2181</t>
+          <t>-74.22765</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>74010</t>
+          <t>629675</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>331JARDIN DE NIÑOS / NUESTRA SEÑORA DE FATIMA</t>
+          <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.16448</t>
+          <t>-13.16322</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.22664</t>
+          <t>-74.2235</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74133</t>
+          <t>73925</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LUIS CARRANZA</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.15696</t>
+          <t>-13.16039</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.22479</t>
+          <t>-74.22819</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74147</t>
+          <t>74675</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.15031</t>
+          <t>-13.158519</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.22324</t>
+          <t>-74.227247</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>533927</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38006 9 DE DICIEMBRE</t>
+          <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.15892</t>
+          <t>-13.12064</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.224053</t>
+          <t>-74.2317</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74166</t>
+          <t>558404</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38018 / 38018 DE MARAVILLAS</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.15254</t>
+          <t>-13.16185</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.22561</t>
+          <t>-74.2275</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74208</t>
+          <t>74430</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LOS LIBERTADORES</t>
+          <t>FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.15725</t>
+          <t>-13.162192</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.23076</t>
+          <t>-74.23324</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>74227</t>
+          <t>558753</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38001 GUSTAVO CASTRO PANTOJA</t>
+          <t>38984-15 SAN JUAN DE LA FRONTERA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.16038</t>
+          <t>-13.129448</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.2277</t>
+          <t>-74.226835</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MELITON CARVAJAL</t>
+          <t>38059 ABILIO SOTO YUPANQUI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.16403</t>
+          <t>-13.15826</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.2338</t>
+          <t>-74.235</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>74265</t>
+          <t>74878</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38059 ABILIO SOTO YUPANQUI</t>
+          <t>LEONARDO DA VINCI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.15826</t>
+          <t>-13.1592</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.235</t>
+          <t>-74.22828</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>572773</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39001 MARISCAL SUCRE</t>
+          <t>CARICIAS Y TERNURAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.16193</t>
+          <t>-13.1551</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.22536</t>
+          <t>-74.2293</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>74289</t>
+          <t>558531</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39002 MARIA PARADO DE BELLIDO / MARIA PARADO DE BELIDO</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.15927</t>
+          <t>-13.16532</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.22838</t>
+          <t>-74.22931</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74294</t>
+          <t>858544</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39003 CORAZON DE JESUS</t>
+          <t>CENTER</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.15366</t>
+          <t>-13.15642</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.23147</t>
+          <t>-74.22682</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>74147</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>MARISCAL CACERES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.17085</t>
+          <t>-13.15031</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.22765</t>
+          <t>-74.22324</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74430</t>
+          <t>865182</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FRANCISCO BOLOGNESI</t>
+          <t>EL TAMBOR DE HOJALATA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.162192</t>
+          <t>-13.15653</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.23324</t>
+          <t>-74.22686</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>74557</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.14571</t>
+          <t>-13.15647</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.22733</t>
+          <t>-74.22567</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>384507</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>39007 SEÑOR DE AGONIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.15647</t>
+          <t>-13.15339</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.22567</t>
+          <t>-74.21884</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>GUAMAN POMA DE AYALA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.15919</t>
+          <t>-13.14966</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-74.22801</t>
+          <t>-74.2181</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>660</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74637</t>
+          <t>754829</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CESAR ABRAHAM VALLEJO</t>
+          <t>COAR AYACUCHO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.1601</t>
+          <t>-13.17009</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.22106</t>
+          <t>-74.22819</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74642</t>
+          <t>865158</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FEDERICO FROEBEL</t>
+          <t>CYBERNET</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.14883</t>
+          <t>-13.168671</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.22832</t>
+          <t>-74.227322</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>569</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74656</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE HUAMANGA</t>
+          <t>39001 MARISCAL SUCRE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.16366</t>
+          <t>-13.16193</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-74.22599</t>
+          <t>-74.22536</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>507</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74661</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.16004</t>
+          <t>-13.16472</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-74.22431</t>
+          <t>-74.22872</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>74675</t>
+          <t>74703</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.158519</t>
+          <t>-13.15667</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-74.227247</t>
+          <t>-74.22546</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>854579</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>LOBACHEVSKI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.16472</t>
+          <t>-13.15589</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-74.22872</t>
+          <t>-74.22627</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>74468</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.15667</t>
+          <t>-13.14571</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-74.22546</t>
+          <t>-74.22733</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>636</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>74878</t>
+          <t>630754</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LEONARDO DA VINCI</t>
+          <t>432-91</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.1592</t>
+          <t>-13.15728</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-74.22828</t>
+          <t>-74.23635</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>74166</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38582 ABRAHAM VALDELOMAR</t>
+          <t>38018 / 38018 DE MARAVILLAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.1806</t>
+          <t>-13.15254</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-74.221</t>
+          <t>-74.22561</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>639</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76047</t>
+          <t>74637</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>38037 LIBERTAD DE AMERICA / LIBERTAD DE AMERICA</t>
+          <t>CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.053175</t>
+          <t>-13.1601</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-74.140672</t>
+          <t>-74.22106</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,27 +2361,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>193522</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>38984-12 CARLOS LABORDE</t>
+          <t>39003 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.13955</t>
+          <t>-13.15366</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-74.22659</t>
+          <t>-74.23147</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>753</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>384507</t>
+          <t>74581</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>39007 SEÑOR DE AGONIA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-13.15339</t>
+          <t>-13.15919</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-74.21884</t>
+          <t>-74.22801</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>697</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>397963</t>
+          <t>193522</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>38984-12 CARLOS LABORDE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-13.166</t>
+          <t>-13.13955</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-74.22751</t>
+          <t>-74.22659</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>641</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>533927</t>
+          <t>690371</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
+          <t>LOS LICENCIADOS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-13.12064</t>
+          <t>-13.14587</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-74.2317</t>
+          <t>-74.22923</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>593</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>558404</t>
+          <t>558480</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-13.16185</t>
+          <t>-13.15732</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-74.2275</t>
+          <t>-74.225</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>703</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>558480</t>
+          <t>558847</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>REPUBLICA BOLIVARIANA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-13.15732</t>
+          <t>-13.135569</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-74.225</t>
+          <t>-74.232699</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>727</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>558531</t>
+          <t>74661</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-13.16532</t>
+          <t>-13.16004</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-74.22931</t>
+          <t>-74.22431</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>950</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>558753</t>
+          <t>74246</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>38984-15 SAN JUAN DE LA FRONTERA</t>
+          <t>MELITON CARVAJAL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-13.129448</t>
+          <t>-13.16403</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-74.226835</t>
+          <t>-74.2338</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>921</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>558847</t>
+          <t>74289</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>REPUBLICA BOLIVARIANA DE VENEZUELA</t>
+          <t>39002 MARIA PARADO DE BELLIDO / MARIA PARADO DE BELIDO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-13.135569</t>
+          <t>-13.15927</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-74.232699</t>
+          <t>-74.22838</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>883</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>572773</t>
+          <t>622037</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CARICIAS Y TERNURAS</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-13.1551</t>
+          <t>-13.14993</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-74.2293</t>
+          <t>-74.22572</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>622037</t>
+          <t>74227</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>38001 GUSTAVO CASTRO PANTOJA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-13.14993</t>
+          <t>-13.16038</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-74.22572</t>
+          <t>-74.2277</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>629675</t>
+          <t>76047</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS</t>
+          <t>38037 LIBERTAD DE AMERICA / LIBERTAD DE AMERICA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-13.16322</t>
+          <t>-13.053175</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-74.2235</t>
+          <t>-74.140672</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>617</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>630754</t>
+          <t>74656</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>432-91</t>
+          <t>SAN ANTONIO DE HUAMANGA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-13.15728</t>
+          <t>-13.16366</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-74.23635</t>
+          <t>-74.22599</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>937</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>690371</t>
+          <t>75415</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LOS LICENCIADOS</t>
+          <t>38582 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-13.14587</t>
+          <t>-13.1806</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-74.22923</t>
+          <t>-74.221</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>754829</t>
+          <t>74642</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>COAR AYACUCHO</t>
+          <t>FEDERICO FROEBEL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-13.17009</t>
+          <t>-13.14883</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-74.22819</t>
+          <t>-74.22832</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>854292</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>38006 9 DE DICIEMBRE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-13.14993</t>
+          <t>-13.15892</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-74.22575</t>
+          <t>-74.224053</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>854579</t>
+          <t>74208</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LOBACHEVSKI</t>
+          <t>LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-13.15589</t>
+          <t>-13.15725</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-74.22627</t>
+          <t>-74.23076</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>858544</t>
+          <t>74010</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CENTER</t>
+          <t>331JARDIN DE NIÑOS / NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-13.15642</t>
+          <t>-13.16448</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-74.22682</t>
+          <t>-74.22664</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>865158</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CYBERNET</t>
+          <t>LUIS CARRANZA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-13.168671</t>
+          <t>-13.15696</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-74.227322</t>
+          <t>-74.22479</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>865182</t>
+          <t>854292</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EL TAMBOR DE HOJALATA</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-13.15653</t>
+          <t>-13.14993</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-74.22686</t>
+          <t>-74.22575</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">

--- a/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>397963</t>
+          <t>865182</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>EL TAMBOR DE HOJALATA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.166</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.22751</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-13.15653</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-74.22686</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>865158</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>CYBERNET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.17085</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.22765</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>-13.168671</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>-74.227322</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73987</t>
+          <t>858544</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>320 SAN MIGUELITO ARCANGEL</t>
+          <t>CENTER</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.15368</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.22856</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-13.15642</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.22682</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>629675</t>
+          <t>854579</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS</t>
+          <t>LOBACHEVSKI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.16322</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.2235</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-13.15589</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.22627</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73925</t>
+          <t>854292</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.16039</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.22819</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-13.14993</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.22575</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74675</t>
+          <t>754829</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>COAR AYACUCHO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.158519</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.227247</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-13.17009</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.22819</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>533927</t>
+          <t>690371</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
+          <t>LOS LICENCIADOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.12064</t>
+          <t>593</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.2317</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-13.14587</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.22923</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>558404</t>
+          <t>630754</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>432-91</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.16185</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.2275</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-13.15728</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.23635</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74430</t>
+          <t>629675</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FRANCISCO BOLOGNESI</t>
+          <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.162192</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.23324</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-13.16322</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-74.2235</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>558753</t>
+          <t>622037</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38984-15 SAN JUAN DE LA FRONTERA</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.129448</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.226835</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-13.14993</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-74.22572</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>74265</t>
+          <t>572773</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38059 ABILIO SOTO YUPANQUI</t>
+          <t>CARICIAS Y TERNURAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.15826</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.235</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-13.1551</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.2293</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>74878</t>
+          <t>558847</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LEONARDO DA VINCI</t>
+          <t>REPUBLICA BOLIVARIANA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.1592</t>
+          <t>727</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.22828</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-13.135569</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.232699</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>572773</t>
+          <t>558753</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CARICIAS Y TERNURAS</t>
+          <t>38984-15 SAN JUAN DE LA FRONTERA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.1551</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.2293</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-13.129448</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.226835</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>-13.16532</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-74.22931</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>858544</t>
+          <t>558480</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CENTER</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.15642</t>
+          <t>703</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.22682</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-13.15732</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-74.225</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74147</t>
+          <t>558404</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.15031</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.22324</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>-13.16185</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>-74.2275</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>865182</t>
+          <t>533927</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EL TAMBOR DE HOJALATA</t>
+          <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.15653</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.22686</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-13.12064</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-74.2317</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>397963</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.15647</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.22567</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-13.166</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-74.22751</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>-13.15339</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-74.21884</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>193522</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GUAMAN POMA DE AYALA</t>
+          <t>38984-12 CARLOS LABORDE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.14966</t>
+          <t>641</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-74.2181</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>-13.13955</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-74.22659</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>754829</t>
+          <t>076047</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COAR AYACUCHO</t>
+          <t>38037 LIBERTAD DE AMERICA / LIBERTAD DE AMERICA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.17009</t>
+          <t>617</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.22819</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-13.053175</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-74.140672</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>865158</t>
+          <t>075415</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CYBERNET</t>
+          <t>38582 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.168671</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.227322</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>-13.1806</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-74.221</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>074878</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>39001 MARISCAL SUCRE</t>
+          <t>LEONARDO DA VINCI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.16193</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-74.22536</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>-13.1592</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-74.22828</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>074703</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.16472</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-74.22872</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-13.15667</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-74.22546</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>074699</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.15667</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-74.22546</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-13.16472</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-74.22872</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>854579</t>
+          <t>074675</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LOBACHEVSKI</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.15589</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-74.22627</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-13.158519</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-74.227247</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>074661</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.14571</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-74.22733</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>-13.16004</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-74.22431</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>630754</t>
+          <t>074656</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>432-91</t>
+          <t>SAN ANTONIO DE HUAMANGA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.15728</t>
+          <t>937</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-74.23635</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-13.16366</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-74.22599</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74166</t>
+          <t>074642</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38018 / 38018 DE MARAVILLAS</t>
+          <t>FEDERICO FROEBEL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.15254</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-74.22561</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>-13.14883</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-74.22832</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>74637</t>
+          <t>074637</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2309,22 +2309,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>-13.1601</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-74.22106</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>74294</t>
+          <t>074581</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>39003 CORAZON DE JESUS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.15366</t>
+          <t>697</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-74.23147</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>-13.15919</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.22801</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>074557</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-13.15919</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-74.22801</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>-13.15647</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.22567</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>193522</t>
+          <t>074468</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>38984-12 CARLOS LABORDE</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-13.13955</t>
+          <t>636</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-74.22659</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>-13.14571</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.22733</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>690371</t>
+          <t>074430</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LOS LICENCIADOS</t>
+          <t>FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-13.14587</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-74.22923</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>-13.162192</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.23324</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>558480</t>
+          <t>074388</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-13.15732</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-74.225</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>-13.17085</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-74.22765</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>558847</t>
+          <t>074294</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>REPUBLICA BOLIVARIANA DE VENEZUELA</t>
+          <t>39003 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-13.135569</t>
+          <t>753</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-74.232699</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>-13.15366</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-74.23147</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>74661</t>
+          <t>074289</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>39002 MARIA PARADO DE BELLIDO / MARIA PARADO DE BELIDO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-13.16004</t>
+          <t>883</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-74.22431</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>-13.15927</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-74.22838</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>074270</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MELITON CARVAJAL</t>
+          <t>39001 MARISCAL SUCRE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-13.16403</t>
+          <t>507</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-74.2338</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>-13.16193</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-74.22536</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>74289</t>
+          <t>074265</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>39002 MARIA PARADO DE BELLIDO / MARIA PARADO DE BELIDO</t>
+          <t>38059 ABILIO SOTO YUPANQUI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-13.15927</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-74.22838</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>-13.15826</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-74.235</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>622037</t>
+          <t>074246</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>MELITON CARVAJAL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-13.14993</t>
+          <t>921</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-74.22572</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-13.16403</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-74.2338</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>74227</t>
+          <t>074227</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2991,22 +2991,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>-13.16038</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>-74.2277</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>76047</t>
+          <t>074208</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>38037 LIBERTAD DE AMERICA / LIBERTAD DE AMERICA</t>
+          <t>LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-13.053175</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-74.140672</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>-13.15725</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-74.23076</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>74656</t>
+          <t>074166</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE HUAMANGA</t>
+          <t>38018 / 38018 DE MARAVILLAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-13.16366</t>
+          <t>639</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-74.22599</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>-13.15254</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-74.22561</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>074152</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>38582 ABRAHAM VALDELOMAR</t>
+          <t>38006 9 DE DICIEMBRE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-13.1806</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-74.221</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>-13.15892</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-74.224053</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>74642</t>
+          <t>074147</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FEDERICO FROEBEL</t>
+          <t>MARISCAL CACERES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-13.14883</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-74.22832</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>-13.15031</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-74.22324</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>074133</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>38006 9 DE DICIEMBRE</t>
+          <t>LUIS CARRANZA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-13.15892</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-74.224053</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>-13.15696</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-74.22479</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>74208</t>
+          <t>074010</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LOS LIBERTADORES</t>
+          <t>331JARDIN DE NIÑOS / NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-13.15725</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-74.23076</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>-13.16448</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-74.22664</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>74010</t>
+          <t>073987</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>331JARDIN DE NIÑOS / NUESTRA SEÑORA DE FATIMA</t>
+          <t>320 SAN MIGUELITO ARCANGEL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-13.16448</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-74.22664</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>-13.15368</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-74.22856</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>74133</t>
+          <t>073968</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LUIS CARRANZA</t>
+          <t>GUAMAN POMA DE AYALA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-13.15696</t>
+          <t>660</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-74.22479</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>-13.14966</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-74.2181</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>854292</t>
+          <t>073925</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-13.14993</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-74.22575</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-13.16039</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-74.22819</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">

--- a/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
